--- a/桌面轮足/结构/Bom.xlsx
+++ b/桌面轮足/结构/Bom.xlsx
@@ -92,7 +92,7 @@
     <t>M3*8</t>
   </si>
   <si>
-    <t>M3*24</t>
+    <t>M3*25</t>
   </si>
   <si>
     <t>对锁螺栓</t>
@@ -833,7 +833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -877,9 +877,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
@@ -1455,7 +1452,7 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="21"/>
+      <c r="N1" s="20"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
@@ -1851,16 +1848,16 @@
       <c r="P20" s="3"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="6">
         <v>4</v>
       </c>
       <c r="E21" s="3"/>
@@ -1945,7 +1942,7 @@
       </c>
       <c r="E25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="22"/>
+      <c r="J25" s="21"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -2042,7 +2039,7 @@
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="22"/>
+      <c r="J31" s="21"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -2080,7 +2077,7 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="9"/>
-      <c r="B34" s="18"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="I34" s="3"/>
@@ -2112,217 +2109,217 @@
     </row>
     <row r="36" ht="16" customHeight="1" spans="1:16">
       <c r="A36" s="12"/>
-      <c r="B36" s="18"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="12"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
     </row>
     <row r="37" ht="17" customHeight="1" spans="1:16">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:16">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:16">
       <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
     </row>
     <row r="40" ht="19" customHeight="1" spans="1:16">
       <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
     </row>
     <row r="41" ht="13" customHeight="1" spans="1:16">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
     </row>
     <row r="42" ht="12" customHeight="1" spans="1:16">
       <c r="A42" s="5"/>
-      <c r="B42" s="20"/>
+      <c r="B42" s="19"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
     </row>
     <row r="43" ht="13" customHeight="1" spans="5:16">
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
     </row>
     <row r="44" ht="23" spans="5:16">
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
     </row>
     <row r="45" ht="23" spans="5:16">
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19"/>
-      <c r="O45" s="19"/>
-      <c r="P45" s="19"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
     </row>
     <row r="46" ht="23" spans="5:16">
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19"/>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
     </row>
     <row r="47" ht="23" spans="5:16">
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-      <c r="P47" s="19"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
     </row>
     <row r="48" ht="23" spans="1:16">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="19"/>
-      <c r="P48" s="19"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/桌面轮足/结构/Bom.xlsx
+++ b/桌面轮足/结构/Bom.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\newestBalance\balance_robot\桌面轮足\结构\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19120" windowHeight="11520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19120" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
   <si>
     <t>购买清单bom表汇总</t>
   </si>
@@ -140,38 +145,93 @@
     <t>DM3507</t>
   </si>
   <si>
+    <t>——</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM-H3510-1E </t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?spm=a1z10.1-c-s.w137644-23556904997.28.3f5128f6epXOzj&amp;id=767305853444&amp;pisk=fpDiT2x9QfP_D1D52B26MJ0ZYgdRfGwb5qBYk-U2TyzIH5dbBolnVq49cCwttr0E-PWtHRnq-00i6Np_Wi0mcy3AHcHmOtmScAK_Hh6sf-w2yUp8nci_hPWURNMGTprsYtW4_OVwBFw2yUpJeci_h-lYLcadBWzQj1rquPrU8yZcgGu47W7Ucow4ueCD36iweYRgMzbguaMpcEKLPczhEMM3YdakFy6VKvrGyzoNctWqKlVsH6ah7wVtg0NSB29cdRnoTJrmh350o7cqBJkw8LPQgj04AXTcizcqXbMUti-zzAiEFJPpU3mEdVnsKmI23k388cMaUwJbAAnqISDDosszu65rZGBbYnHhG6FaAk4R7GRhDUtKrg-Hxwfb_kZwexKhOv753TiBxHbOQ5rQbdf..&amp;skuId=5440731611045</t>
+  </si>
+  <si>
+    <t>电池</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?_u=b3gud67l3a33&amp;id=527326501663&amp;skuId=4922250528308&amp;spm=a1z09.2.0.0.15f12e8dmRzzzY</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100ma/h 30C</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?ft=t&amp;id=871173947758</t>
+  </si>
+  <si>
     <t>https://item.taobao.com/item.htm?id=855508643710&amp;pisk=fJQyrj0czzUyVu2SfL8Eu7QuI_TJSFe_aw9Bt6fHNLvkFw6FtCdKqB0kZK4DsKgQwUZp89JVpLtWrwSx81CdP7LQwUCJJe2_CPTFw_LdGeb9EazDnQCDtDAhtzDkRe2_Cyoji3eW-T_8DHnWmKdet20hKnvDNKAkteXHnnAMt4YH-URF1WFbf3eGnKjpOTG2zlNBn20hryKyQDJDMI_4t3vNZauE8kdy4dfk3RHgne-c9H7K9281ZGBpsTDuLpQViajGI-iWEGRF1M5urqY5y_jMxN2Kx_TDUEblbX0hgUJVBwXmU-JGysb9onag_sbAF_QVOX4HGO9cwaYUS5LyrLYV4XMpi5tcJgknY3AvgdN4gXVjhtlAQRyivDK4DIJ_65nKv3AvgdN4gDnp0Nd2C5FO.&amp;spm=a1z10.1-c-s.w4004-23563087546.2.c255509fDloIZc</t>
-  </si>
-  <si>
-    <t>——</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM-H3510-1E </t>
-  </si>
-  <si>
-    <t>STM32 H723</t>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?spm=a1z10.1-c-s.w137644-23556904997.28.3f5128f6epXOzj&amp;id=767305853444&amp;pisk=fpDiT2x9QfP_D1D52B26MJ0ZYgdRfGwb5qBYk-U2TyzIH5dbBolnVq49cCwttr0E-PWtHRnq-00i6Np_Wi0mcy3AHcHmOtmScAK_Hh6sf-w2yUp8nci_hPWURNMGTprsYtW4_OVwBFw2yUpJeci_h-lYLcadBWzQj1rquPrU8yZcgGu47W7Ucow4ueCD36iweYRgMzbguaMpcEKLPczhEMM3YdakFy6VKvrGyzoNctWqKlVsH6ah7wVtg0NSB29cdRnoTJrmh350o7cqBJkw8LPQgj04AXTcizcqXbMUti-zzAiEFJPpU3mEdVnsKmI23k388cMaUwJbAAnqISDDosszu65rZGBbYnHhG6FaAk4R7GRhDUtKrg-Hxwfb_kZwexKhOv753TiBxHbOQ5rQbdf..&amp;skuId=5440731611045</t>
-  </si>
-  <si>
-    <t>电池</t>
-  </si>
-  <si>
-    <t>无参考购买链接</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>关节电机/DM-J3507-2EC/转接板/SH1.0转XT30 2+2 · kit/达妙科技 - 码云 - 开源中国</t>
+  </si>
+  <si>
+    <t>sh1.25-8pin转xt30 2+2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>转接板1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>转接板2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>关节电机/DM-J3507-2EC/转接板/SH1.0转XT30 +GH1.25 · kit/达妙科技 - 码云 - 开源中国</t>
+  </si>
+  <si>
+    <t>sh1.25-3pin+8pin转xt30+gh1.25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>转接板1用于实机连线中</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>转接板2用于上位机与电机单独调试</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>转接板1和转接板2可以自己打板，也可以和电机一起购买（在淘宝上选好电机套餐）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝牙模块</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>JDY-33蓝牙从机模块</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?_u=b2085qbuhef29d&amp;id=618317697790&amp;pisk=fRkqoq6ElKpVjkvHloyNUGJaA7VYH-YBSAa_jcmgcr4D6o9GQco3fnL9Dbri54K9D-ig7Vu7yOZ6MFBZzqinGSgsGPqgr4mfhP9Y_VoIJV66HjZGQ4iTsVMZXOrijVKY5nKSDmeTIeTQQpixDcX8SzDVILVo2ofGo3hDIX2TIeTBdpixDR3LmkjUo_quyo7ciVVcE0qTrlf0IV4uZkqCoR0gI35ujlZGS54iq3rUbNX0itfkEkqdmP0gI3SuXXanSqBzzSxK58rQKHKUGym0oisjnGPfMmUyAHHPd1UEm1BGIYr4MAtXMeYaGfmL9xiWQTejYb2uAmpVUJm0YqaS-pXzE0io5WhJW9wjzAPrI7JhzuhocfDxuGWgDxMQ_yFyjOF_EvNn_R8RauGixYPnEhsU5XiSn7uHPTuT_Xn_bqJVn2jPqNEorektgNfgiOZzR3-rjG_urar8e75O67R84ytpv1fGJ961gAtA61FymuzBvnf..&amp;skuId=4590057118482&amp;spm=a1z09.2.0.0.9ead2e8d3vUIM7</t>
+  </si>
+  <si>
+    <t>STM32 H723开发板</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,7 +253,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -201,7 +261,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,135 +280,55 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,194 +341,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -585,255 +379,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -858,7 +413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -867,31 +422,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -900,90 +455,184 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -994,7 +643,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1022,157 +671,213 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1" descr="http://www.kdocs.cn/api/v3/office/copy/RFBSZTlzNnI3OGsxVTlWWXFrcnhqV1FPajhkdHVSQlJUNWg4V0JJVUFaZVdScThocWNtK1JobWJ4VlB2SjBBZDFYK2hYNlFBdVRRMlZjK2laWHpLN0l4MlNMRWovb2tqZmZhZnNNNWdrVjZOdlZ0c1BaTXBaWitDYTB0WG5mNVl0eXFPY3RBcXFDN1ZvUDQzQ2xkWDlxUHBOUzRCMGdTc2JQU0FIaVFvVkRPdzJvU2p2c2x0RUhmekZSbk1mNXp6QWtvTGtOS0lsZmRaRUs5WGZCSXhTN3gvM2pkUkFBa1JaNVNjeWsrU3pGTGlZdFEyb2U0RERDR1FybUJoNVA4U3Yza1NXSm04R3UwPQ==/attach/object/GKJ464Y5ACADO?"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9544050" y="4978400"/>
+          <a:ext cx="374650" cy="279400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2" descr="http://www.kdocs.cn/api/v3/office/copy/RFBSZTlzNnI3OGsxVTlWWXFrcnhqV1FPajhkdHVSQlJUNWg4V0JJVUFaZVdScThocWNtK1JobWJ4VlB2SjBBZDFYK2hYNlFBdVRRMlZjK2laWHpLN0l4MlNMRWovb2tqZmZhZnNNNWdrVjZOdlZ0c1BaTXBaWitDYTB0WG5mNVl0eXFPY3RBcXFDN1ZvUDQzQ2xkWDlxUHBOUzRCMGdTc2JQU0FIaVFvVkRPdzJvU2p2c2x0RUhmekZSbk1mNXp6QWtvTGtOS0lsZmRaRUs5WGZCSXhTN3gvM2pkUkFBa1JaNVNjeWsrU3pGTGlZdFEyb2U0RERDR1FybUJoNVA4U3Yza1NXSm04R3UwPQ==/attach/object/77cf457856fd61952da6328ad4358f6c79ee3540?"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9544050" y="5245100"/>
+          <a:ext cx="190500" cy="279400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3" descr="http://www.kdocs.cn/api/v3/office/copy/RFBSZTlzNnI3OGsxVTlWWXFrcnhqV1FPajhkdHVSQlJUNWg4V0JJVUFaZVdScThocWNtK1JobWJ4VlB2SjBBZDFYK2hYNlFBdVRRMlZjK2laWHpLN0l4MlNMRWovb2tqZmZhZnNNNWdrVjZOdlZ0c1BaTXBaWitDYTB0WG5mNVl0eXFPY3RBcXFDN1ZvUDQzQ2xkWDlxUHBOUzRCMGdTc2JQU0FIaVFvVkRPdzJvU2p2c2x0RUhmekZSbk1mNXp6QWtvTGtOS0lsZmRaRUs5WGZCSXhTN3gvM2pkUkFBa1JaNVNjeWsrU3pGTGlZdFEyb2U0RERDR1FybUJoNVA4U3Yza1NXSm04R3UwPQ==/attach/object/f2643b2cb5c8a21fa94b44936dde4069e5843e9c?"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9544050" y="5867400"/>
+          <a:ext cx="622300" cy="279400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1419,24 +1124,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P48"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="54.8545454545455" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="10" max="10" width="19.2727272727273" customWidth="1"/>
-    <col min="11" max="11" width="21.7272727272727" customWidth="1"/>
-    <col min="14" max="14" width="25.3727272727273" customWidth="1"/>
+    <col min="5" max="5" width="38.54296875" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
+    <col min="11" max="11" width="21.7265625" customWidth="1"/>
+    <col min="14" max="14" width="25.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1456,7 +1162,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1465,7 +1171,12 @@
       <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>59</v>
+      </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -1475,7 +1186,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
@@ -1494,7 +1205,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
@@ -1513,7 +1224,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1532,7 +1243,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
@@ -1555,7 +1266,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>8</v>
       </c>
@@ -1578,7 +1289,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>12</v>
       </c>
@@ -1601,7 +1312,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>15</v>
       </c>
@@ -1624,7 +1335,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>15</v>
       </c>
@@ -1647,7 +1358,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>15</v>
       </c>
@@ -1670,7 +1381,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>15</v>
       </c>
@@ -1693,7 +1404,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>15</v>
       </c>
@@ -1716,7 +1427,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>22</v>
       </c>
@@ -1739,7 +1450,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12"/>
@@ -1754,7 +1465,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
@@ -1769,7 +1480,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -1784,7 +1495,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>25</v>
       </c>
@@ -1801,7 +1512,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>26</v>
       </c>
@@ -1824,7 +1535,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>29</v>
       </c>
@@ -1847,7 +1558,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
@@ -1870,7 +1581,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1885,7 +1596,7 @@
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
@@ -1904,15 +1615,15 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="D24" s="9">
         <v>2</v>
@@ -1927,15 +1638,15 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" s="9">
         <v>2</v>
@@ -1950,22 +1661,14 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+      <c r="J26" s="21"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -1973,11 +1676,20 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -1987,13 +1699,19 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="D28" s="12">
+        <v>1</v>
+      </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -2003,13 +1721,23 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+    <row r="29" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="12">
+        <v>2</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="27"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -2019,11 +1747,23 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="9"/>
+    <row r="30" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="9">
+        <v>1</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="27"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -2033,9 +1773,11 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
-      <c r="B31" s="11"/>
+      <c r="B31" s="24" t="s">
+        <v>54</v>
+      </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="I31" s="3"/>
@@ -2047,7 +1789,7 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="9"/>
@@ -2061,11 +1803,20 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="9"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
+    <row r="33" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="9">
+        <v>1</v>
+      </c>
+      <c r="F33" s="27"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -2075,7 +1826,7 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="17"/>
       <c r="C34" s="9"/>
@@ -2089,7 +1840,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="9"/>
       <c r="C35" s="12"/>
@@ -2107,7 +1858,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" ht="16" customHeight="1" spans="1:16">
+    <row r="36" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="17"/>
       <c r="C36" s="12"/>
@@ -2125,7 +1876,7 @@
       <c r="O36" s="18"/>
       <c r="P36" s="18"/>
     </row>
-    <row r="37" ht="17" customHeight="1" spans="1:16">
+    <row r="37" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -2143,7 +1894,7 @@
       <c r="O37" s="18"/>
       <c r="P37" s="18"/>
     </row>
-    <row r="38" ht="18" customHeight="1" spans="1:16">
+    <row r="38" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2161,7 +1912,7 @@
       <c r="O38" s="18"/>
       <c r="P38" s="18"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:16">
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2179,7 +1930,7 @@
       <c r="O39" s="18"/>
       <c r="P39" s="18"/>
     </row>
-    <row r="40" ht="19" customHeight="1" spans="1:16">
+    <row r="40" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -2197,7 +1948,7 @@
       <c r="O40" s="18"/>
       <c r="P40" s="18"/>
     </row>
-    <row r="41" ht="13" customHeight="1" spans="1:16">
+    <row r="41" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2215,7 +1966,7 @@
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
     </row>
-    <row r="42" ht="12" customHeight="1" spans="1:16">
+    <row r="42" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="19"/>
       <c r="C42" s="6"/>
@@ -2233,7 +1984,7 @@
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
     </row>
-    <row r="43" ht="13" customHeight="1" spans="5:16">
+    <row r="43" spans="1:16" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
       <c r="G43" s="18"/>
@@ -2247,7 +1998,7 @@
       <c r="O43" s="18"/>
       <c r="P43" s="18"/>
     </row>
-    <row r="44" ht="23" spans="5:16">
+    <row r="44" spans="1:16" ht="23" x14ac:dyDescent="0.25">
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="18"/>
@@ -2261,7 +2012,7 @@
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
     </row>
-    <row r="45" ht="23" spans="5:16">
+    <row r="45" spans="1:16" ht="23" x14ac:dyDescent="0.25">
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
       <c r="G45" s="18"/>
@@ -2275,7 +2026,7 @@
       <c r="O45" s="18"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" ht="23" spans="5:16">
+    <row r="46" spans="1:16" ht="23" x14ac:dyDescent="0.25">
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
       <c r="G46" s="18"/>
@@ -2289,7 +2040,7 @@
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" ht="23" spans="5:16">
+    <row r="47" spans="1:16" ht="23" x14ac:dyDescent="0.25">
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
       <c r="G47" s="18"/>
@@ -2303,7 +2054,7 @@
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
     </row>
-    <row r="48" ht="23" spans="1:16">
+    <row r="48" spans="1:16" ht="23" x14ac:dyDescent="0.25">
       <c r="A48" s="18"/>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -2322,24 +2073,29 @@
       <c r="P48" s="18"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B24" r:id="rId1" display="https://item.taobao.com/item.htm?id=855508643710&amp;pisk=fJQyrj0czzUyVu2SfL8Eu7QuI_TJSFe_aw9Bt6fHNLvkFw6FtCdKqB0kZK4DsKgQwUZp89JVpLtWrwSx81CdP7LQwUCJJe2_CPTFw_LdGeb9EazDnQCDtDAhtzDkRe2_Cyoji3eW-T_8DHnWmKdet20hKnvDNKAkteXHnnAMt4YH-URF1WFbf3eGnKjpOTG2zlNBn20hryKyQDJDMI_4t3vNZauE8kdy4dfk3RHgne-c9H7K9281ZGBpsTDuLpQViajGI-iWEGRF1M5urqY5y_jMxN2Kx_TDUEblbX0hgUJVBwXmU-JGysb9onag_sbAF_QVOX4HGO9cwaYUS5LyrLYV4XMpi5tcJgknY3AvgdN4gXVjhtlAQRyivDK4DIJ_65nKv3AvgdN4gDnp0Nd2C5FO.&amp;spm=a1z10.1-c-s.w4004-23563087546.2.c255509fDloIZc" tooltip="https://item.taobao.com/item.htm?id=855508643710&amp;pisk=fJQyrj0czzUyVu2SfL8Eu7QuI_TJSFe_aw9Bt6fHNLvkFw6FtCdKqB0kZK4DsKgQwUZp89JVpLtWrwSx81CdP7LQwUCJJe2_CPTFw_LdGeb9EazDnQCDtDAhtzDkRe2_Cyoji3eW-T_8DHnWmKdet20hKnvDNKAkteXHnnAMt4YH-URF1WFbf3eGnKjpOTG2zlNBn20hr"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
-    <hyperlink ref="B19" r:id="rId3" display="https://detail.tmall.com/item.htm?id=617808114995&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe67ee&amp;pisk=fhYx0Zby0YDc-RiMlIilSjrdm_hlHEd2aKRQSOX0fLpJBBFDmGXGfNpepGai0ZjOWL6kotAcl1s6IptchnXgWFpyHr4Gld0OCB-r_tfDo5C6VKUMmIXD25Q2rn4Gnx791pbtKv0n-IRVbNMnKv1q6V_C_Sa_IGg5PJXYiDgn-IR8isGHN2cZpLsCd1_1cG6SPT5T5l_6Cg65OTaf1r1_FbCNFO_1c1aSP61b5osfCbEEMTPfMPK6W87Z94ijBALRNAWBMr4l6F1Yv9AcevaJyeSAdI685v4y1p6OUeMo2QJpcKfyB2HRRHJJWM_tkJ5vVBQ5nwiL2Zdk3eQXJxUcZaX5Ahs-GqORktI1gM3thZK63FI2D5leNZ9yY9Sj4Y5JoejOLgeShQARhMK9nYz1nHdWeMYuEybBYLLOAwsPUeYpkgyhp1qjwbEabi1uAcUuE7iHabCRKjsbblSGa_BnwTrabg_Ow9cxLlrNVfC..&amp;skuId=4355692940487"/>
-    <hyperlink ref="B6" r:id="rId4" display="https://detail.tmall.com/item.htm?id=534828257082&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhef350&amp;pisk=fsSS01AcEbc5kS6XtUe2l6gazy-CN_Zavv9dI9nrp3KJRDBP1poe8zvIAI6TEQz3r6_f9sYywB8eAp1wiToUETyQA9B9wH7yapCVOs0PaMRFgk6G1UoPpMklo1Wt4gzkYDtkxHFa_lrNUTxHvG0lT4lkHdvaY0nJe4ZfU-Pa_lrQyxKQN57FMbKkhpOvepd-y-tvIdRpvedJD-9pLb3K26BYhpAve2p-yjHvId9-vbEmGpzWpTwxDU7gw8cGPIiKfAvWy5Wq8ci_cLYk6EKqv-SXFUOOegjeqppA0iTwuvP2DObVwKt_Vfv5kOtJdM2tRBTCqnOf1lnHnaC5Des4KlBJVpT9vEMKvttfzEpWXlhXnZBPJgfSdDpl4G8BsEwKxe-AbFQONv2GH3pdtFjUs0ARpOjG7hZSsL_ACnsz_cRsr10IhFmBhCybh20EduI2b5lh2NTJnLEah-Gj-UpDhRebhV4ByKvWe-wjS61.."/>
+    <hyperlink ref="B24"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
+    <hyperlink ref="B19" r:id="rId2" display="https://detail.tmall.com/item.htm?id=617808114995&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe67ee&amp;pisk=fhYx0Zby0YDc-RiMlIilSjrdm_hlHEd2aKRQSOX0fLpJBBFDmGXGfNpepGai0ZjOWL6kotAcl1s6IptchnXgWFpyHr4Gld0OCB-r_tfDo5C6VKUMmIXD25Q2rn4Gnx791pbtKv0n-IRVbNMnKv1q6V_C_Sa_IGg5PJXYiDgn-IR8isGHN2cZpLsCd1_1cG6SPT5T5l_6Cg65OTaf1r1_FbCNFO_1c1aSP61b5osfCbEEMTPfMPK6W87Z94ijBALRNAWBMr4l6F1Yv9AcevaJyeSAdI685v4y1p6OUeMo2QJpcKfyB2HRRHJJWM_tkJ5vVBQ5nwiL2Zdk3eQXJxUcZaX5Ahs-GqORktI1gM3thZK63FI2D5leNZ9yY9Sj4Y5JoejOLgeShQARhMK9nYz1nHdWeMYuEybBYLLOAwsPUeYpkgyhp1qjwbEabi1uAcUuE7iHabCRKjsbblSGa_BnwTrabg_Ow9cxLlrNVfC..&amp;skuId=4355692940487"/>
+    <hyperlink ref="B6" r:id="rId3" display="https://detail.tmall.com/item.htm?id=534828257082&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhef350&amp;pisk=fsSS01AcEbc5kS6XtUe2l6gazy-CN_Zavv9dI9nrp3KJRDBP1poe8zvIAI6TEQz3r6_f9sYywB8eAp1wiToUETyQA9B9wH7yapCVOs0PaMRFgk6G1UoPpMklo1Wt4gzkYDtkxHFa_lrNUTxHvG0lT4lkHdvaY0nJe4ZfU-Pa_lrQyxKQN57FMbKkhpOvepd-y-tvIdRpvedJD-9pLb3K26BYhpAve2p-yjHvId9-vbEmGpzWpTwxDU7gw8cGPIiKfAvWy5Wq8ci_cLYk6EKqv-SXFUOOegjeqppA0iTwuvP2DObVwKt_Vfv5kOtJdM2tRBTCqnOf1lnHnaC5Des4KlBJVpT9vEMKvttfzEpWXlhXnZBPJgfSdDpl4G8BsEwKxe-AbFQONv2GH3pdtFjUs0ARpOjG7hZSsL_ACnsz_cRsr10IhFmBhCybh20EduI2b5lh2NTJnLEah-Gj-UpDhRebhV4ByKvWe-wjS61.."/>
     <hyperlink ref="B7" r:id="rId4" display="https://detail.tmall.com/item.htm?id=534828257082&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhef350&amp;pisk=fsSS01AcEbc5kS6XtUe2l6gazy-CN_Zavv9dI9nrp3KJRDBP1poe8zvIAI6TEQz3r6_f9sYywB8eAp1wiToUETyQA9B9wH7yapCVOs0PaMRFgk6G1UoPpMklo1Wt4gzkYDtkxHFa_lrNUTxHvG0lT4lkHdvaY0nJe4ZfU-Pa_lrQyxKQN57FMbKkhpOvepd-y-tvIdRpvedJD-9pLb3K26BYhpAve2p-yjHvId9-vbEmGpzWpTwxDU7gw8cGPIiKfAvWy5Wq8ci_cLYk6EKqv-SXFUOOegjeqppA0iTwuvP2DObVwKt_Vfv5kOtJdM2tRBTCqnOf1lnHnaC5Des4KlBJVpT9vEMKvttfzEpWXlhXnZBPJgfSdDpl4G8BsEwKxe-AbFQONv2GH3pdtFjUs0ARpOjG7hZSsL_ACnsz_cRsr10IhFmBhCybh20EduI2b5lh2NTJnLEah-Gj-UpDhRebhV4ByKvWe-wjS61.."/>
-    <hyperlink ref="B5" r:id="rId2" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
-    <hyperlink ref="B8" r:id="rId5" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=673367228604&amp;rn=c2a32b0ae8e4624b2e8f4e8f2e719e3e&amp;spm=a1z10.3-b.w4011-14789405706.40.7e6037bauDUWS3"/>
-    <hyperlink ref="B9" r:id="rId6" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=636175026159&amp;rn=d62e44d01be55868af98aa2eff1e3e44&amp;spm=a1z10.3-b.w4011-14789405706.82.7e6037bagSsNWc"/>
-    <hyperlink ref="B10" r:id="rId6" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=636175026159&amp;rn=d62e44d01be55868af98aa2eff1e3e44&amp;spm=a1z10.3-b.w4011-14789405706.82.7e6037bagSsNWc"/>
-    <hyperlink ref="B11" r:id="rId6" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=636175026159&amp;rn=d62e44d01be55868af98aa2eff1e3e44&amp;spm=a1z10.3-b.w4011-14789405706.82.7e6037bagSsNWc"/>
-    <hyperlink ref="B12" r:id="rId6" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=636175026159&amp;rn=d62e44d01be55868af98aa2eff1e3e44&amp;spm=a1z10.3-b.w4011-14789405706.82.7e6037bagSsNWc"/>
-    <hyperlink ref="B14" r:id="rId7" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=775683678140&amp;rn=291ab2023ac9aea42a1fd1cb6d48dd4d&amp;skuId=5473489626659&amp;spm=a1z10.3-b.w4011-14789405706.57.7e6037ba0Ys1WN" tooltip="https://detail.tmall.com/item.htm?abbucket=10&amp;id=775683678140&amp;rn=291ab2023ac9aea42a1fd1cb6d48dd4d&amp;skuId=5473489626659&amp;spm=a1z10.3-b.w4011-14789405706.57.7e6037ba0Ys1WN"/>
-    <hyperlink ref="B13" r:id="rId6" display="https://detail.tmall.com/item.htm?abbucket=10&amp;id=636175026159&amp;rn=d62e44d01be55868af98aa2eff1e3e44&amp;spm=a1z10.3-b.w4011-14789405706.82.7e6037bagSsNWc"/>
-    <hyperlink ref="B4" r:id="rId2" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
-    <hyperlink ref="B21" r:id="rId8" display="https://detail.tmall.com/item.htm?abbucket=19&amp;id=666300049176&amp;pisk=gGyqv09u3tBqAAZUPJDwLtukReMxpA7QIRgsjlqicq0cMmgwSruWCj1Y5GPzSzhjoZCxjdz3yctbjRigQxe7GdgfkArgRA7CR96QDohtIw_I3g12jvmIjIYsSUDoCclKENh4DoHtS3TGO7qv7lb6eFmiSgkobDviIfvDZgosjIDiofYuqc0oIV4iiTmoDcoMsAvgqgoEACvmIAqoqmiwoC4iIgroycDimb_QSrprzjjgW_ikkpgtg2qmzpr8UmmwMouyNQezaju3d4JMI8o4VWdfip5s-W3jO24lFKkaqczrOS7e3Prgv5czQEjb-zVaS0FR7CuUsoNLejxMiuyZuX2maHjLYomgSfPR8piqh7lU3SI9ro4IuWDYfH7b4XPr90ckbIDbOkwtt-X2J4GKbzlQgwJ4-gW9W0DWwRF2SClm20uC4gy22NVAZD3tcCdta_nrRMIp6Chmy0uC2id96bYq42svw&amp;rn=39c004adf2e35f950877eb755a407750&amp;spm=a1z10.5-b-s.w4011-22722948235.55.28063254pj6sG8&amp;skuId=4978407875180"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
+    <hyperlink ref="B8" r:id="rId6"/>
+    <hyperlink ref="B9" r:id="rId7"/>
+    <hyperlink ref="B10" r:id="rId8"/>
+    <hyperlink ref="B11" r:id="rId9"/>
+    <hyperlink ref="B12" r:id="rId10"/>
+    <hyperlink ref="B14" r:id="rId11" tooltip="https://detail.tmall.com/item.htm?abbucket=10&amp;id=775683678140&amp;rn=291ab2023ac9aea42a1fd1cb6d48dd4d&amp;skuId=5473489626659&amp;spm=a1z10.3-b.w4011-14789405706.57.7e6037ba0Ys1WN"/>
+    <hyperlink ref="B13" r:id="rId12"/>
+    <hyperlink ref="B4" r:id="rId13" display="https://detail.tmall.com/item.htm?id=693377485791&amp;spm=a1z09.2.0.0.31ac2e8dkAjhS8&amp;_u=12085qbuhe5af5&amp;pisk=fqcm0vmBNxybPaQ9mbVXB7WCS8v-GiNs_cCTX5EwUurW5tBvlRzZScctHVrTscmijoewcShiq2g9lfLbgC4Zv0VtkoEtqFmx51KXCSCNjmgecqE9lfqaqmogCEZTblmt7xLJ9B3jl5NajHdp9y1-Vqmc_5W277zY5Y3VHwujl5ZNyGJKUq6M0z8s_Roaa8zao5z4bPuyrP41_5r4QgWz8ura_5oaaTzLoiSabrPzzbUA3khZLb-4KNn9zfWZkr20j1ElsmcC9Rqe2u5Gso0_nx34q15ZZY9jqWq2daE_Mog4ocOCGSyiQjFrg3RaTviosJPHBEwqSYm_Mb8N3kkxDRGuEiW4-Sq0LjyD1ENzQYcuMj-1d43u0JV-eLtYBSmmdkw2F3iironZi8SD2lHKyjyoY3CofRDZM7l24BjyzTWEyC1_zFhPCOw4PzqILGGF55gxHH8kr93_3zaQvUYlCD24Pr22rUXCS-z7on5.."/>
+    <hyperlink ref="B21" r:id="rId14" display="https://detail.tmall.com/item.htm?abbucket=19&amp;id=666300049176&amp;pisk=gGyqv09u3tBqAAZUPJDwLtukReMxpA7QIRgsjlqicq0cMmgwSruWCj1Y5GPzSzhjoZCxjdz3yctbjRigQxe7GdgfkArgRA7CR96QDohtIw_I3g12jvmIjIYsSUDoCclKENh4DoHtS3TGO7qv7lb6eFmiSgkobDviIfvDZgosjIDiofYuqc0oIV4iiTmoDcoMsAvgqgoEACvmIAqoqmiwoC4iIgroycDimb_QSrprzjjgW_ikkpgtg2qmzpr8UmmwMouyNQezaju3d4JMI8o4VWdfip5s-W3jO24lFKkaqczrOS7e3Prgv5czQEjb-zVaS0FR7CuUsoNLejxMiuyZuX2maHjLYomgSfPR8piqh7lU3SI9ro4IuWDYfH7b4XPr90ckbIDbOkwtt-X2J4GKbzlQgwJ4-gW9W0DWwRF2SClm20uC4gy22NVAZD3tcCdta_nrRMIp6Chmy0uC2id96bYq42svw&amp;rn=39c004adf2e35f950877eb755a407750&amp;spm=a1z10.5-b-s.w4011-22722948235.55.28063254pj6sG8&amp;skuId=4978407875180"/>
+    <hyperlink ref="B28" r:id="rId15"/>
+    <hyperlink ref="B29" r:id="rId16" display="https://gitee.com/kit-miao/damiao/tree/master/%E5%85%B3%E8%8A%82%E7%94%B5%E6%9C%BA/DM-J3507-2EC/%E8%BD%AC%E6%8E%A5%E6%9D%BF/SH1.0%E8%BD%ACXT30 2+2"/>
+    <hyperlink ref="B30" r:id="rId17" display="https://gitee.com/kit-miao/damiao/tree/master/%E5%85%B3%E8%8A%82%E7%94%B5%E6%9C%BA/DM-J3507-2EC/%E8%BD%AC%E6%8E%A5%E6%9D%BF/SH1.0%E8%BD%ACXT30 +GH1.25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>